--- a/Uploads/francais_validate_requete .xlsx
+++ b/Uploads/francais_validate_requete .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\ChamberAppel\Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0979433-8994-4C0B-A4AD-AF09F60FE218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F345D262-576F-40C1-9A89-04F0CEA442E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,9 +52,6 @@
     <t>2024-09-06</t>
   </si>
   <si>
-    <t>وكيل 1</t>
-  </si>
-  <si>
     <t>خازن 1</t>
   </si>
   <si>
@@ -139,9 +136,6 @@
     <t>مستشار خلف 2</t>
   </si>
   <si>
-    <t>وكيل 2</t>
-  </si>
-  <si>
     <t>خازن 2</t>
   </si>
   <si>
@@ -178,9 +172,6 @@
     <t>مستشار خلف 3</t>
   </si>
   <si>
-    <t>وكيل 3</t>
-  </si>
-  <si>
     <t>خازن 3</t>
   </si>
   <si>
@@ -217,9 +208,6 @@
     <t>مستشار خلف 4</t>
   </si>
   <si>
-    <t>وكيل 4</t>
-  </si>
-  <si>
     <t>خازن 4</t>
   </si>
   <si>
@@ -256,9 +244,6 @@
     <t>مستشار خلف 5</t>
   </si>
   <si>
-    <t>وكيل 5</t>
-  </si>
-  <si>
     <t>خازن 5</t>
   </si>
   <si>
@@ -295,9 +280,6 @@
     <t>مستشار خلف 6</t>
   </si>
   <si>
-    <t>وكيل 6</t>
-  </si>
-  <si>
     <t>خازن 6</t>
   </si>
   <si>
@@ -334,9 +316,6 @@
     <t>مستشار خلف 7</t>
   </si>
   <si>
-    <t>وكيل 7</t>
-  </si>
-  <si>
     <t>خازن 7</t>
   </si>
   <si>
@@ -373,9 +352,6 @@
     <t>مستشار خلف 8</t>
   </si>
   <si>
-    <t>وكيل 8</t>
-  </si>
-  <si>
     <t>خازن 8</t>
   </si>
   <si>
@@ -412,9 +388,6 @@
     <t>مستشار خلف 9</t>
   </si>
   <si>
-    <t>وكيل 9</t>
-  </si>
-  <si>
     <t>خازن 9</t>
   </si>
   <si>
@@ -451,9 +424,6 @@
     <t>مستشار خلف 10</t>
   </si>
   <si>
-    <t>وكيل 10</t>
-  </si>
-  <si>
     <t>خازن 10</t>
   </si>
   <si>
@@ -779,6 +749,36 @@
   </si>
   <si>
     <t>2342</t>
+  </si>
+  <si>
+    <t>منطوق القرار  1</t>
+  </si>
+  <si>
+    <t>منطوق القرار  2</t>
+  </si>
+  <si>
+    <t>منطوق القرار  3</t>
+  </si>
+  <si>
+    <t>منطوق القرار  4</t>
+  </si>
+  <si>
+    <t>منطوق القرار  5</t>
+  </si>
+  <si>
+    <t>منطوق القرار  6</t>
+  </si>
+  <si>
+    <t>منطوق القرار  7</t>
+  </si>
+  <si>
+    <t>منطوق القرار  8</t>
+  </si>
+  <si>
+    <t>منطوق القرار  9</t>
+  </si>
+  <si>
+    <t>منطوق القرار  10</t>
   </si>
 </sst>
 </file>
@@ -1193,12 +1193,12 @@
     <col min="18" max="18" width="42" customWidth="1"/>
     <col min="19" max="19" width="39.28515625" customWidth="1"/>
     <col min="20" max="20" width="75" customWidth="1"/>
-    <col min="21" max="21" width="39.140625" customWidth="1"/>
-    <col min="22" max="22" width="29.42578125" customWidth="1"/>
-    <col min="23" max="23" width="28.42578125" customWidth="1"/>
-    <col min="24" max="24" width="50.140625" customWidth="1"/>
-    <col min="25" max="25" width="37.85546875" customWidth="1"/>
-    <col min="26" max="26" width="31.5703125" customWidth="1"/>
+    <col min="21" max="21" width="63.28515625" customWidth="1"/>
+    <col min="22" max="22" width="60.5703125" customWidth="1"/>
+    <col min="23" max="23" width="63.28515625" customWidth="1"/>
+    <col min="24" max="24" width="83.85546875" customWidth="1"/>
+    <col min="25" max="25" width="55.7109375" customWidth="1"/>
+    <col min="26" max="26" width="59.42578125" customWidth="1"/>
     <col min="27" max="27" width="66.85546875" customWidth="1"/>
     <col min="28" max="28" width="59.85546875" customWidth="1"/>
     <col min="29" max="29" width="52.7109375" customWidth="1"/>
@@ -1222,139 +1222,139 @@
   <sheetData>
     <row r="1" spans="1:45" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="U1" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="V1" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="W1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="O1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="R1" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="S1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AE1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="AF1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="AG1" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="AH1" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI1" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="AJ1" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK1" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="AL1" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="AM1" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="AN1" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="AO1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="AP1" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="AQ1" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="Y1" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="AO1" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="AP1" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="AR1" s="4" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="AS1" s="4" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
@@ -1371,7 +1371,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>4</v>
@@ -1397,118 +1397,118 @@
       <c r="M2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC2" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AE2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AF2" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="AG2" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF2" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AH2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="AI2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH2" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="AI2" s="3" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AK2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AL2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL2" s="3" t="s">
+      <c r="AM2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AN2" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="AO2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="AN2" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AP2" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="AR2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AS2" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AP2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="AR2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="AS2" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>4</v>
@@ -1520,132 +1520,132 @@
         <v>5</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="T3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="Y3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="T3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y3" s="2" t="s">
+      <c r="AA3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Z3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="AB3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC3" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="AG3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF3" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AH3" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="AI3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+      <c r="AK3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL3" s="3" t="s">
+      <c r="AM3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM3" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN3" s="2" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="AO3" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AP3" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="AS3" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="AR3" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="AS3" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>4</v>
@@ -1657,132 +1657,132 @@
         <v>5</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q4" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q4" s="2" t="s">
+      <c r="T4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X4" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="T4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X4" s="2" t="s">
+      <c r="AA4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="Y4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="AB4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="AD4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC4" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AE4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE4" s="3" t="s">
+      <c r="AF4" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="AG4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF4" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="AG4" s="3" t="s">
+      <c r="AH4" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AI4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH4" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="AI4" s="3" t="s">
+      <c r="AJ4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ4" s="3" t="s">
+      <c r="AK4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK4" s="3" t="s">
+      <c r="AL4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL4" s="3" t="s">
+      <c r="AM4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM4" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN4" s="2" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="AO4" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AP4" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="AS4" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AQ4" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="AR4" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="AS4" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>4</v>
@@ -1794,132 +1794,132 @@
         <v>5</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="2" t="s">
+      <c r="T5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="Z5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="AA5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="T5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="AB5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="AD5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC5" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AE5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE5" s="3" t="s">
+      <c r="AF5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF5" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AH5" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="AI5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH5" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="AI5" s="3" t="s">
+      <c r="AJ5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ5" s="3" t="s">
+      <c r="AK5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK5" s="3" t="s">
+      <c r="AL5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL5" s="3" t="s">
+      <c r="AM5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM5" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN5" s="2" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="AO5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AP5" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="AR5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="AQ5" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="AR5" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="AS5" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>4</v>
@@ -1931,132 +1931,132 @@
         <v>5</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="T6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="2" t="s">
+      <c r="Y6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Z6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="AA6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="T6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA6" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="AB6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="AD6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="AD6" s="3" t="s">
+      <c r="AE6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE6" s="3" t="s">
+      <c r="AF6" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="AG6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="AG6" s="3" t="s">
+      <c r="AH6" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="AI6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH6" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="AI6" s="3" t="s">
+      <c r="AJ6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ6" s="3" t="s">
+      <c r="AK6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK6" s="3" t="s">
+      <c r="AL6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL6" s="3" t="s">
+      <c r="AM6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM6" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN6" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="AO6" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="AP6" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="AR6" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AS6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AQ6" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="AR6" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="AS6" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>4</v>
@@ -2068,132 +2068,132 @@
         <v>5</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X7" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="Y7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="2" t="s">
+      <c r="Z7" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q7" s="2" t="s">
+      <c r="AA7" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="AB7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AD7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="AD7" s="3" t="s">
+      <c r="AE7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE7" s="3" t="s">
+      <c r="AF7" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="AG7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF7" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="AG7" s="3" t="s">
+      <c r="AH7" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="AI7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH7" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="AI7" s="3" t="s">
+      <c r="AJ7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ7" s="3" t="s">
+      <c r="AK7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK7" s="3" t="s">
+      <c r="AL7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL7" s="3" t="s">
+      <c r="AM7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM7" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN7" s="2" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="AO7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AP7" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="AR7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS7" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AQ7" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="AR7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="AS7" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>4</v>
@@ -2205,132 +2205,132 @@
         <v>5</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA8" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="AB8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="AD8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD8" s="3" t="s">
+      <c r="AE8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE8" s="3" t="s">
+      <c r="AF8" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG8" s="3" t="s">
+      <c r="AH8" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH8" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="AI8" s="3" t="s">
+      <c r="AJ8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ8" s="3" t="s">
+      <c r="AK8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK8" s="3" t="s">
+      <c r="AL8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL8" s="3" t="s">
+      <c r="AM8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM8" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="AO8" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="AO8" s="3" t="s">
+      <c r="AP8" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="AP8" s="3" t="s">
+      <c r="AR8" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="AS8" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AQ8" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="AR8" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="AS8" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>4</v>
@@ -2342,132 +2342,132 @@
         <v>5</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="AA9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="AB9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="AD9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="AD9" s="3" t="s">
+      <c r="AE9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE9" s="3" t="s">
+      <c r="AF9" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="AG9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="AG9" s="3" t="s">
+      <c r="AH9" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AI9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH9" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AI9" s="3" t="s">
+      <c r="AJ9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ9" s="3" t="s">
+      <c r="AK9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK9" s="3" t="s">
+      <c r="AL9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL9" s="3" t="s">
+      <c r="AM9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM9" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="AO9" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="AO9" s="3" t="s">
+      <c r="AP9" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="AP9" s="3" t="s">
+      <c r="AR9" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AS9" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AQ9" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="AR9" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="AS9" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>4</v>
@@ -2479,132 +2479,132 @@
         <v>5</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K10" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA10" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="AB10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="AD10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="AD10" s="3" t="s">
+      <c r="AE10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE10" s="3" t="s">
+      <c r="AF10" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="AG10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="AG10" s="3" t="s">
+      <c r="AH10" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="AI10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH10" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="AI10" s="3" t="s">
+      <c r="AJ10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ10" s="3" t="s">
+      <c r="AK10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK10" s="3" t="s">
+      <c r="AL10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL10" s="3" t="s">
+      <c r="AM10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM10" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="AO10" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="AO10" s="3" t="s">
+      <c r="AP10" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="AP10" s="3" t="s">
+      <c r="AR10" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="AS10" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AQ10" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="AR10" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="AS10" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>4</v>
@@ -2616,115 +2616,115 @@
         <v>5</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>7</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="2" t="s">
-        <v>143</v>
+      <c r="N11" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="T11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="U11" s="3" t="s">
+      <c r="V11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="V11" s="3" t="s">
+      <c r="W11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W11" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="X11" s="2" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="AD11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="AC11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="AD11" s="3" t="s">
+      <c r="AE11" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="AE11" s="3" t="s">
+      <c r="AF11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AF11" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="AG11" s="3" t="s">
+      <c r="AH11" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AI11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AH11" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI11" s="3" t="s">
+      <c r="AJ11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AJ11" s="3" t="s">
+      <c r="AK11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AK11" s="3" t="s">
+      <c r="AL11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AL11" s="3" t="s">
+      <c r="AM11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="AM11" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="AN11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="AO11" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="AO11" s="3" t="s">
+      <c r="AP11" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="AP11" s="3" t="s">
+      <c r="AR11" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="AS11" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="AQ11" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="AR11" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="AS11" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/francais_validate_requete .xlsx
+++ b/Uploads/francais_validate_requete .xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\ChamberAppel\Uploads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\ChamberAppel\Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F345D262-576F-40C1-9A89-04F0CEA442E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5F3D63-8D9A-418A-9816-CE88D2B14E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="249">
   <si>
     <t>1</t>
   </si>
@@ -707,18 +707,6 @@
   </si>
   <si>
     <t>2024-09-28</t>
-  </si>
-  <si>
-    <t>2024-09-30</t>
-  </si>
-  <si>
-    <t>2024-09-31</t>
-  </si>
-  <si>
-    <t>2024-09-32</t>
-  </si>
-  <si>
-    <t>2024-09-33</t>
   </si>
   <si>
     <t>2333</t>
@@ -1173,54 +1161,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AS11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="3" max="3" width="49.42578125" customWidth="1"/>
-    <col min="4" max="4" width="33.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" customWidth="1"/>
+    <col min="3" max="3" width="49.453125" customWidth="1"/>
+    <col min="4" max="4" width="33.54296875" customWidth="1"/>
     <col min="5" max="6" width="67" customWidth="1"/>
-    <col min="7" max="7" width="32.42578125" customWidth="1"/>
-    <col min="8" max="8" width="77.85546875" customWidth="1"/>
-    <col min="9" max="9" width="28.28515625" customWidth="1"/>
-    <col min="10" max="10" width="90.5703125" customWidth="1"/>
-    <col min="11" max="11" width="62.42578125" customWidth="1"/>
-    <col min="12" max="12" width="53.85546875" customWidth="1"/>
-    <col min="13" max="13" width="67.140625" customWidth="1"/>
-    <col min="14" max="14" width="51.7109375" customWidth="1"/>
-    <col min="15" max="16" width="47.85546875" customWidth="1"/>
-    <col min="17" max="17" width="36.5703125" customWidth="1"/>
+    <col min="7" max="7" width="32.453125" customWidth="1"/>
+    <col min="8" max="8" width="77.81640625" customWidth="1"/>
+    <col min="9" max="9" width="28.26953125" customWidth="1"/>
+    <col min="10" max="10" width="90.54296875" customWidth="1"/>
+    <col min="11" max="11" width="62.453125" customWidth="1"/>
+    <col min="12" max="12" width="53.81640625" customWidth="1"/>
+    <col min="13" max="13" width="67.1796875" customWidth="1"/>
+    <col min="14" max="14" width="51.7265625" customWidth="1"/>
+    <col min="15" max="16" width="47.81640625" customWidth="1"/>
+    <col min="17" max="17" width="36.54296875" customWidth="1"/>
     <col min="18" max="18" width="42" customWidth="1"/>
-    <col min="19" max="19" width="39.28515625" customWidth="1"/>
+    <col min="19" max="19" width="39.26953125" customWidth="1"/>
     <col min="20" max="20" width="75" customWidth="1"/>
-    <col min="21" max="21" width="63.28515625" customWidth="1"/>
-    <col min="22" max="22" width="60.5703125" customWidth="1"/>
-    <col min="23" max="23" width="63.28515625" customWidth="1"/>
-    <col min="24" max="24" width="83.85546875" customWidth="1"/>
-    <col min="25" max="25" width="55.7109375" customWidth="1"/>
-    <col min="26" max="26" width="59.42578125" customWidth="1"/>
-    <col min="27" max="27" width="66.85546875" customWidth="1"/>
-    <col min="28" max="28" width="59.85546875" customWidth="1"/>
-    <col min="29" max="29" width="52.7109375" customWidth="1"/>
-    <col min="30" max="30" width="57.42578125" customWidth="1"/>
-    <col min="31" max="31" width="36.85546875" customWidth="1"/>
-    <col min="32" max="32" width="49.28515625" customWidth="1"/>
-    <col min="33" max="33" width="54.85546875" customWidth="1"/>
-    <col min="34" max="34" width="50.85546875" customWidth="1"/>
-    <col min="35" max="35" width="57.42578125" customWidth="1"/>
-    <col min="36" max="37" width="53.42578125" customWidth="1"/>
-    <col min="38" max="38" width="54.140625" customWidth="1"/>
-    <col min="39" max="39" width="41.85546875" customWidth="1"/>
-    <col min="40" max="40" width="62.85546875" customWidth="1"/>
-    <col min="41" max="41" width="58.7109375" customWidth="1"/>
+    <col min="21" max="21" width="63.26953125" customWidth="1"/>
+    <col min="22" max="22" width="60.54296875" customWidth="1"/>
+    <col min="23" max="23" width="63.26953125" customWidth="1"/>
+    <col min="24" max="24" width="83.81640625" customWidth="1"/>
+    <col min="25" max="25" width="55.7265625" customWidth="1"/>
+    <col min="26" max="26" width="59.453125" customWidth="1"/>
+    <col min="27" max="27" width="66.81640625" customWidth="1"/>
+    <col min="28" max="28" width="59.81640625" customWidth="1"/>
+    <col min="29" max="29" width="52.7265625" customWidth="1"/>
+    <col min="30" max="30" width="57.453125" customWidth="1"/>
+    <col min="31" max="31" width="36.81640625" customWidth="1"/>
+    <col min="32" max="32" width="49.26953125" customWidth="1"/>
+    <col min="33" max="33" width="54.81640625" customWidth="1"/>
+    <col min="34" max="34" width="50.81640625" customWidth="1"/>
+    <col min="35" max="35" width="57.453125" customWidth="1"/>
+    <col min="36" max="37" width="53.453125" customWidth="1"/>
+    <col min="38" max="38" width="54.1796875" customWidth="1"/>
+    <col min="39" max="39" width="41.81640625" customWidth="1"/>
+    <col min="40" max="40" width="62.81640625" customWidth="1"/>
+    <col min="41" max="41" width="58.7265625" customWidth="1"/>
     <col min="42" max="42" width="41" customWidth="1"/>
-    <col min="43" max="43" width="67.140625" customWidth="1"/>
-    <col min="44" max="44" width="76.140625" customWidth="1"/>
-    <col min="45" max="45" width="89.28515625" customWidth="1"/>
-    <col min="46" max="46" width="8.7109375" customWidth="1"/>
+    <col min="43" max="43" width="67.1796875" customWidth="1"/>
+    <col min="44" max="44" width="76.1796875" customWidth="1"/>
+    <col min="45" max="45" width="89.26953125" customWidth="1"/>
+    <col min="46" max="46" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="5" customFormat="1" ht="29.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" s="5" customFormat="1" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>170</v>
       </c>
@@ -1357,7 +1345,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1482,10 +1470,10 @@
         <v>30</v>
       </c>
       <c r="AP2" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="AR2" s="3" t="s">
         <v>30</v>
@@ -1494,7 +1482,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>33</v>
       </c>
@@ -1619,10 +1607,10 @@
         <v>226</v>
       </c>
       <c r="AP3" s="3" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="AQ3" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AR3" s="3" t="s">
         <v>226</v>
@@ -1631,7 +1619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>45</v>
       </c>
@@ -1756,10 +1744,10 @@
         <v>227</v>
       </c>
       <c r="AP4" s="3" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="AQ4" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AR4" s="3" t="s">
         <v>227</v>
@@ -1768,7 +1756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>57</v>
       </c>
@@ -1893,10 +1881,10 @@
         <v>31</v>
       </c>
       <c r="AP5" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AQ5" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="AR5" s="3" t="s">
         <v>31</v>
@@ -1905,7 +1893,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>69</v>
       </c>
@@ -2030,10 +2018,10 @@
         <v>228</v>
       </c>
       <c r="AP6" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AQ6" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="AR6" s="3" t="s">
         <v>228</v>
@@ -2042,7 +2030,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>81</v>
       </c>
@@ -2164,13 +2152,13 @@
         <v>218</v>
       </c>
       <c r="AO7" s="3" t="s">
-        <v>32</v>
+        <v>228</v>
       </c>
       <c r="AP7" s="3" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AQ7" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AR7" s="3" t="s">
         <v>32</v>
@@ -2179,7 +2167,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>93</v>
       </c>
@@ -2301,22 +2289,22 @@
         <v>219</v>
       </c>
       <c r="AO8" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AP8" s="3" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AQ8" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AR8" s="3" t="s">
-        <v>229</v>
+        <v>32</v>
       </c>
       <c r="AS8" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>105</v>
       </c>
@@ -2438,22 +2426,22 @@
         <v>220</v>
       </c>
       <c r="AO9" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AP9" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AQ9" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AR9" s="3" t="s">
-        <v>230</v>
+        <v>32</v>
       </c>
       <c r="AS9" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>117</v>
       </c>
@@ -2575,22 +2563,22 @@
         <v>221</v>
       </c>
       <c r="AO10" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="AP10" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="AQ10" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AR10" s="3" t="s">
-        <v>231</v>
+        <v>32</v>
       </c>
       <c r="AS10" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>129</v>
       </c>
@@ -2712,16 +2700,16 @@
         <v>222</v>
       </c>
       <c r="AO11" s="3" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="AP11" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="AQ11" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AR11" s="3" t="s">
-        <v>232</v>
+        <v>32</v>
       </c>
       <c r="AS11" s="3" t="s">
         <v>31</v>
